--- a/Учет_вагонов_с_тестовыми_данными.xlsx
+++ b/Учет_вагонов_с_тестовыми_данными.xlsx
@@ -902,7 +902,7 @@
         <v>200</v>
       </c>
       <c r="H2" s="3">
-        <f>XLOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="I2" s="3">
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="X2" s="4">
-        <f>IFERROR(MAXIFS(tblПлатежи[Дата платежа],tblПлатежи[ID вагона],[@[ID вагона]],tblПлатежи[Статус],"факт"),"")</f>
+        <f>IFERROR(SUMPRODUCT(MAX((tblПлатежи[ID вагона]=[@[ID вагона]])*(tblПлатежи[Статус]="факт")*(tblПлатежи[Дата платежа]))),"")</f>
         <v/>
       </c>
       <c r="Y2" s="4" t="n">
@@ -1005,7 +1005,7 @@
         <v>205</v>
       </c>
       <c r="H3" s="3">
-        <f>XLOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="I3" s="3">
@@ -1069,7 +1069,7 @@
         <v/>
       </c>
       <c r="X3" s="4">
-        <f>IFERROR(MAXIFS(tblПлатежи[Дата платежа],tblПлатежи[ID вагона],[@[ID вагона]],tblПлатежи[Статус],"факт"),"")</f>
+        <f>IFERROR(SUMPRODUCT(MAX((tblПлатежи[ID вагона]=[@[ID вагона]])*(tblПлатежи[Статус]="факт")*(tblПлатежи[Дата платежа]))),"")</f>
         <v/>
       </c>
       <c r="Y3" s="4" t="n">
@@ -1108,7 +1108,7 @@
         <v>210</v>
       </c>
       <c r="H4" s="3">
-        <f>XLOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата фиксации цены]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="I4" s="3">
@@ -1172,7 +1172,7 @@
         <v/>
       </c>
       <c r="X4" s="4">
-        <f>IFERROR(MAXIFS(tblПлатежи[Дата платежа],tblПлатежи[ID вагона],[@[ID вагона]],tblПлатежи[Статус],"факт"),"")</f>
+        <f>IFERROR(SUMPRODUCT(MAX((tblПлатежи[ID вагона]=[@[ID вагона]])*(tblПлатежи[Статус]="факт")*(tblПлатежи[Дата платежа]))),"")</f>
         <v/>
       </c>
       <c r="Y4" s="4" t="n">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="E2" s="2">
-        <f>XLOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="F2" s="3">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="J2">
-        <f>COUNTIF($B$2:[@[ID вагона]],[@[ID вагона]])</f>
+        <f>COUNTIF(INDEX(tblПлатежи[ID вагона],1):[@[ID вагона]],[@[ID вагона]])</f>
         <v/>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="E3" s="2">
-        <f>XLOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="F3" s="3">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="J3">
-        <f>COUNTIF($B$2:[@[ID вагона]],[@[ID вагона]])</f>
+        <f>COUNTIF(INDEX(tblПлатежи[ID вагона],1):[@[ID вагона]],[@[ID вагона]])</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="E4" s="2">
-        <f>XLOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="F4" s="3">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="J4">
-        <f>COUNTIF($B$2:[@[ID вагона]],[@[ID вагона]])</f>
+        <f>COUNTIF(INDEX(tblПлатежи[ID вагона],1):[@[ID вагона]],[@[ID вагона]])</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <f>XLOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="F5" s="3">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J5">
-        <f>COUNTIF($B$2:[@[ID вагона]],[@[ID вагона]])</f>
+        <f>COUNTIF(INDEX(tblПлатежи[ID вагона],1):[@[ID вагона]],[@[ID вагона]])</f>
         <v/>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="E6" s="2">
-        <f>XLOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс],,-1)</f>
+        <f>LOOKUP([@[Дата платежа]],tblКурсы[Дата],tblКурсы[Курс])</f>
         <v/>
       </c>
       <c r="F6" s="3">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6">
-        <f>COUNTIF($B$2:[@[ID вагона]],[@[ID вагона]])</f>
+        <f>COUNTIF(INDEX(tblПлатежи[ID вагона],1):[@[ID вагона]],[@[ID вагона]])</f>
         <v/>
       </c>
     </row>
